--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_14/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_14/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>42.40177907096175</v>
+        <v>99.99999906265903</v>
       </c>
       <c r="B2" t="n">
-        <v>115.0476357447716</v>
+        <v>124.6653276764369</v>
       </c>
       <c r="C2" t="n">
-        <v>47.71884366769421</v>
+        <v>45.50003347480325</v>
       </c>
       <c r="D2" t="n">
-        <v>6.964431857324951</v>
+        <v>6.25277805273261</v>
       </c>
       <c r="E2" t="n">
-        <v>3.028704243703436</v>
+        <v>4.877411129213814</v>
       </c>
       <c r="F2" t="n">
-        <v>4.261493190313614</v>
+        <v>13.06122947830028</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3991517605122522</v>
+        <v>0.01922065665586417</v>
       </c>
       <c r="H2" t="n">
-        <v>-6.954205581189098e-05</v>
+        <v>-0.903814849975714</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5407473125273964</v>
+        <v>-0.9338208056907081</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.07486266246805351</v>
+        <v>-0.9583969052266059</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.001907371992986968</v>
+        <v>-0.0001713934593041914</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5315504411854312</v>
+        <v>-0.5874999933214455</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02428894678122321</v>
+        <v>-7.438845166241048e-06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>42.40177907096175</v>
+        <v>44.4903616706851</v>
       </c>
       <c r="B3" t="n">
-        <v>115.0529914634448</v>
+        <v>125.1650263522084</v>
       </c>
       <c r="C3" t="n">
-        <v>47.71884366769421</v>
+        <v>45.50040576736203</v>
       </c>
       <c r="D3" t="n">
-        <v>6.964431857324951</v>
+        <v>10.89259364722904</v>
       </c>
       <c r="E3" t="n">
-        <v>3.035114576990277</v>
+        <v>4.608832361491563</v>
       </c>
       <c r="F3" t="n">
-        <v>4.261493190313614</v>
+        <v>4.562195032539481</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3991517605122522</v>
+        <v>0.3543055275736025</v>
       </c>
       <c r="H3" t="n">
-        <v>-6.954205581189098e-05</v>
+        <v>-0.0004255891008984285</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5407473125273964</v>
+        <v>-0.5396387706512332</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.07486266246805351</v>
+        <v>-0.07501491866105987</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.001907371992986968</v>
+        <v>-0.001255009107871026</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5315504411854312</v>
+        <v>-0.2086777125301382</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.02428894678122321</v>
+        <v>-9.017052489734834e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99.99987502294495</v>
+        <v>99.99999906265903</v>
       </c>
       <c r="B4" t="n">
-        <v>116.7761560277405</v>
+        <v>124.6653276764369</v>
       </c>
       <c r="C4" t="n">
-        <v>47.50173554588574</v>
+        <v>45.50003347480325</v>
       </c>
       <c r="D4" t="n">
-        <v>5.544507401502852</v>
+        <v>6.25277805273261</v>
       </c>
       <c r="E4" t="n">
-        <v>4.853360801789578</v>
+        <v>4.66441952828185</v>
       </c>
       <c r="F4" t="n">
-        <v>12.85393753291506</v>
+        <v>13.06122947830028</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0195136606847057</v>
+        <v>0.01922065665586417</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9154111562576055</v>
+        <v>-0.903814849975714</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9411786706950566</v>
+        <v>-0.9338208056907081</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9648480487829546</v>
+        <v>-0.9583969052266059</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.006719082934468338</v>
+        <v>-0.0001713934593041914</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6220060394067202</v>
+        <v>-0.5874999933214455</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0312758856277635</v>
+        <v>-7.438845166241048e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>67.40327662794714</v>
+        <v>44.4903616706851</v>
       </c>
       <c r="B5" t="n">
-        <v>101.4876850085183</v>
+        <v>124.6891990843487</v>
       </c>
       <c r="C5" t="n">
-        <v>47.76127418136985</v>
+        <v>45.50040576736203</v>
       </c>
       <c r="D5" t="n">
-        <v>8.901892899930919</v>
+        <v>10.89259364722904</v>
       </c>
       <c r="E5" t="n">
-        <v>4.875371417922259</v>
+        <v>4.610829066545584</v>
       </c>
       <c r="F5" t="n">
-        <v>7.178403628076593</v>
+        <v>4.562195032539481</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07606090067696822</v>
+        <v>0.3543055275736025</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.7395243215932636</v>
+        <v>-0.0004255891008984285</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8413577500537061</v>
+        <v>-0.5396387706512332</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8443620587096267</v>
+        <v>-0.07501491866105987</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.004472395101317981</v>
+        <v>-0.001255009107871026</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3785071764372244</v>
+        <v>-0.2086777125301382</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.02363930200785447</v>
+        <v>-9.017052489734834e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>69.4685767624696</v>
+        <v>60.38218103950151</v>
       </c>
       <c r="B6" t="n">
-        <v>100.8133206100301</v>
+        <v>127.87164485573</v>
       </c>
       <c r="C6" t="n">
-        <v>47.46511767335706</v>
+        <v>45.50602629174846</v>
       </c>
       <c r="D6" t="n">
-        <v>9.103143887866668</v>
+        <v>9.909084725355187</v>
       </c>
       <c r="E6" t="n">
-        <v>2.844333288727041</v>
+        <v>4.899316691462984</v>
       </c>
       <c r="F6" t="n">
-        <v>7.558891216630231</v>
+        <v>6.32450554474284</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06841879743511006</v>
+        <v>0.1117625433478377</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7611876718529739</v>
+        <v>-0.589065460171093</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8524355687227312</v>
+        <v>-0.7693193612825047</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8612616693037075</v>
+        <v>-0.7153008197474676</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07930642329021459</v>
+        <v>-0.0001023779930455324</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3939351124553624</v>
+        <v>-0.3052230399064483</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.03254091727614634</v>
+        <v>-0.001339175944102405</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>58.37390064961615</v>
+        <v>56.99431428425132</v>
       </c>
       <c r="B7" t="n">
-        <v>117.452559948994</v>
+        <v>124.6891990843487</v>
       </c>
       <c r="C7" t="n">
-        <v>46.5951150537924</v>
+        <v>45.50596699351026</v>
       </c>
       <c r="D7" t="n">
-        <v>10.17968957513034</v>
+        <v>10.44484763264218</v>
       </c>
       <c r="E7" t="n">
-        <v>3.005011276164307</v>
+        <v>4.610829066545584</v>
       </c>
       <c r="F7" t="n">
-        <v>6.117179684530502</v>
+        <v>5.965737390536075</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1297343087200481</v>
+        <v>0.1388762929493997</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6030362741108207</v>
+        <v>-0.5127157756455397</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7756754480423331</v>
+        <v>-0.7355204441989717</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7276745916318259</v>
+        <v>-0.6429132592809109</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.08607343239130442</v>
+        <v>-0.05340405230348599</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3110571082612437</v>
+        <v>-0.2810844892752906</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.04821250557148225</v>
+        <v>-0.001325998557834829</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56.5887065684602</v>
+        <v>45.1288418625741</v>
       </c>
       <c r="B8" t="n">
-        <v>117.452559948994</v>
+        <v>124.5248974257203</v>
       </c>
       <c r="C8" t="n">
-        <v>47.64290026357714</v>
+        <v>45.50031701850889</v>
       </c>
       <c r="D8" t="n">
-        <v>9.906077883918638</v>
+        <v>10.89261174701184</v>
       </c>
       <c r="E8" t="n">
-        <v>3.005011276164307</v>
+        <v>4.712236948609575</v>
       </c>
       <c r="F8" t="n">
-        <v>5.822597927052599</v>
+        <v>4.629605214319962</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1451502787143467</v>
+        <v>0.3355491987643038</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5655172406143492</v>
+        <v>-0.04171631892921627</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7588572576414041</v>
+        <v>-0.5542355040133695</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6930356709137333</v>
+        <v>-0.1254780316334362</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02892233840240013</v>
+        <v>-0.009728162381328606</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2977215839935318</v>
+        <v>-0.2134663139693057</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.02599505204419879</v>
+        <v>-7.044855753146617e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>75.89915950746992</v>
+        <v>95.86222165841544</v>
       </c>
       <c r="B9" t="n">
-        <v>114.4282121733199</v>
+        <v>117.620834271583</v>
       </c>
       <c r="C9" t="n">
-        <v>47.73594895375225</v>
+        <v>43.03130891520344</v>
       </c>
       <c r="D9" t="n">
-        <v>8.183049744195374</v>
+        <v>8.636221222024332</v>
       </c>
       <c r="E9" t="n">
-        <v>3.596015882068103</v>
+        <v>4.697713804782795</v>
       </c>
       <c r="F9" t="n">
-        <v>8.450649130137753</v>
+        <v>12.66575996898271</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04974433307053677</v>
+        <v>0.02227042230052486</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.815230200449284</v>
+        <v>-0.8913723863358509</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8814535330830118</v>
+        <v>-0.9258134716282448</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.901263034653552</v>
+        <v>-0.9511179104298191</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.01059291550428794</v>
+        <v>-0.3580094928010157</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4419720139646662</v>
+        <v>-0.55801832931621</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0240712926806611</v>
+        <v>-0.3327800966381087</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>78.15780946509965</v>
+        <v>78.04677794058536</v>
       </c>
       <c r="B10" t="n">
-        <v>119.3113528144555</v>
+        <v>105.8638386444084</v>
       </c>
       <c r="C10" t="n">
-        <v>43.31034855082443</v>
+        <v>45.50044822258458</v>
       </c>
       <c r="D10" t="n">
-        <v>8.39172190469967</v>
+        <v>8.507814717889058</v>
       </c>
       <c r="E10" t="n">
-        <v>2.702969984444576</v>
+        <v>4.750579075591454</v>
       </c>
       <c r="F10" t="n">
-        <v>8.901719813091994</v>
+        <v>8.918135439030692</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04499534150166138</v>
+        <v>0.04434358088112768</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8300427899827405</v>
+        <v>-0.8053207603429565</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8896831283728114</v>
+        <v>-0.8759359145229103</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9115906421259615</v>
+        <v>-0.8943101716536294</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01601231434021003</v>
+        <v>-0.008133945241641774</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.458844286643687</v>
+        <v>-0.4310832928266707</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.08564793380026364</v>
+        <v>-9.96050187965225e-05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>47.01572574803888</v>
+        <v>81.19608230616436</v>
       </c>
       <c r="B11" t="n">
-        <v>98.40872197457733</v>
+        <v>139.610347466583</v>
       </c>
       <c r="C11" t="n">
-        <v>47.75760205190434</v>
+        <v>45.50040807370989</v>
       </c>
       <c r="D11" t="n">
-        <v>6.760077097400546</v>
+        <v>8.344312134615802</v>
       </c>
       <c r="E11" t="n">
-        <v>3.879357680377084</v>
+        <v>4.680913678779981</v>
       </c>
       <c r="F11" t="n">
-        <v>4.863163024475982</v>
+        <v>9.475477205367413</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2697340804902536</v>
+        <v>0.03867063031104463</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2631384803652831</v>
+        <v>-0.8262317891002022</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6368872466320569</v>
+        <v>-0.8875106614230657</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.3834702547966404</v>
+        <v>-0.909070116693414</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.07483374167417266</v>
+        <v>-0.03630134951968136</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.562187333103647</v>
+        <v>-0.453522086431421</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.02378057617794165</v>
+        <v>-9.068304664183735e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>45.53226350378431</v>
+        <v>90.87089390339807</v>
       </c>
       <c r="B12" t="n">
-        <v>101.088932228479</v>
+        <v>115.5294792627127</v>
       </c>
       <c r="C12" t="n">
-        <v>47.64226172817931</v>
+        <v>45.52338105099217</v>
       </c>
       <c r="D12" t="n">
-        <v>6.723633805954364</v>
+        <v>7.953749368219442</v>
       </c>
       <c r="E12" t="n">
-        <v>2.609053843007749</v>
+        <v>4.54386901824003</v>
       </c>
       <c r="F12" t="n">
-        <v>4.642840853643497</v>
+        <v>11.35752784266463</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3042693841922815</v>
+        <v>0.02642865921951548</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1901099536147657</v>
+        <v>-0.8738961642234179</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6093619390908004</v>
+        <v>-0.915196425988571</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3009932607680607</v>
+        <v>-0.9404908985743865</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.01914138981809861</v>
+        <v>-0.1674619240930639</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5523370518535889</v>
+        <v>-0.5224551190617112</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.02602026772964526</v>
+        <v>-0.005195789109371379</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>92.09549692312326</v>
+        <v>93.96230418161346</v>
       </c>
       <c r="B13" t="n">
-        <v>117.6968014737866</v>
+        <v>107.9036751858232</v>
       </c>
       <c r="C13" t="n">
-        <v>46.14322563392956</v>
+        <v>45.52333361491539</v>
       </c>
       <c r="D13" t="n">
-        <v>6.758728330717523</v>
+        <v>7.958838809884475</v>
       </c>
       <c r="E13" t="n">
-        <v>2.860485441221509</v>
+        <v>4.890579410844086</v>
       </c>
       <c r="F13" t="n">
-        <v>11.32975364195965</v>
+        <v>12.03172791031882</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02561818950235718</v>
+        <v>0.02367378518746235</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8934641882307152</v>
+        <v>-0.885243063783592</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9272970167857577</v>
+        <v>-0.9220975379447959</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.9523320128586642</v>
+        <v>-0.947458389080047</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.04582429421819028</v>
+        <v>-0.2410537428212456</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.5629597838292387</v>
+        <v>-0.5444814172939958</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.04494520188592436</v>
+        <v>-0.005185247758977274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>74.09638636912283</v>
+        <v>49.72547661576154</v>
       </c>
       <c r="B14" t="n">
-        <v>114.3593628990777</v>
+        <v>120.8608568359609</v>
       </c>
       <c r="C14" t="n">
-        <v>47.73948290028448</v>
+        <v>45.50042667654558</v>
       </c>
       <c r="D14" t="n">
-        <v>8.477471585780682</v>
+        <v>10.88417460822924</v>
       </c>
       <c r="E14" t="n">
-        <v>2.178734985110749</v>
+        <v>4.610829066545584</v>
       </c>
       <c r="F14" t="n">
-        <v>8.196213520102088</v>
+        <v>5.141546022652827</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05421139598614617</v>
+        <v>0.2322145653037172</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8019319646537543</v>
+        <v>-0.2710690823591324</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8741396785257309</v>
+        <v>-0.6370892825353416</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8917368966113018</v>
+        <v>-0.3900631455713152</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.04071186519340086</v>
+        <v>-0.03624064319098263</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4285051729139501</v>
+        <v>-0.2292940208873009</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.02402632541432619</v>
+        <v>-9.481701012850619e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>90.06356221809337</v>
+        <v>49.10530726961387</v>
       </c>
       <c r="B15" t="n">
-        <v>98.09415968377283</v>
+        <v>120.7436033596936</v>
       </c>
       <c r="C15" t="n">
-        <v>43.478181266246</v>
+        <v>45.50553438702937</v>
       </c>
       <c r="D15" t="n">
-        <v>7.081309910887833</v>
+        <v>10.84196464108662</v>
       </c>
       <c r="E15" t="n">
-        <v>2.797613853271644</v>
+        <v>4.714513754727649</v>
       </c>
       <c r="F15" t="n">
-        <v>10.97023897502535</v>
+        <v>5.060944922732184</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02762331290937858</v>
+        <v>0.243380629245196</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8865293448406261</v>
+        <v>-0.2534552223203611</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9229790583627969</v>
+        <v>-0.6321838582234166</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.9481889660924193</v>
+        <v>-0.3725203725658703</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01151440790696843</v>
+        <v>-0.03740117883025043</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5477810898959796</v>
+        <v>-0.2340825594090514</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.07864181018909948</v>
+        <v>-0.001229863784304314</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>44.98217196724568</v>
+        <v>76.05387514481188</v>
       </c>
       <c r="B16" t="n">
-        <v>85.40376171596529</v>
+        <v>123.4872678728507</v>
       </c>
       <c r="C16" t="n">
-        <v>47.75704068364192</v>
+        <v>45.50004588599703</v>
       </c>
       <c r="D16" t="n">
-        <v>6.737298198647114</v>
+        <v>8.759931830639319</v>
       </c>
       <c r="E16" t="n">
-        <v>2.86916923162449</v>
+        <v>4.983375907328377</v>
       </c>
       <c r="F16" t="n">
-        <v>4.566661398225661</v>
+        <v>8.607938422546532</v>
       </c>
       <c r="G16" t="n">
-        <v>0.3185743000904931</v>
+        <v>0.04858091816202457</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.160518943812336</v>
+        <v>-0.7902011660206357</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5984067230206352</v>
+        <v>-0.8677325181269804</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2668458723243315</v>
+        <v>-0.8832981380841881</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.009461433525739586</v>
+        <v>-0.02559607504610309</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5486844099551056</v>
+        <v>-0.4168838604067846</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.02380217313854198</v>
+        <v>-1.019688822823106e-05</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>49.61972509956024</v>
+        <v>62.66503974327728</v>
       </c>
       <c r="B17" t="n">
-        <v>102.8695849407451</v>
+        <v>124.9158917823839</v>
       </c>
       <c r="C17" t="n">
-        <v>46.02074476892072</v>
+        <v>45.61920863954618</v>
       </c>
       <c r="D17" t="n">
-        <v>6.404914206729525</v>
+        <v>9.906676465173456</v>
       </c>
       <c r="E17" t="n">
-        <v>2.425162171858498</v>
+        <v>4.707353693382434</v>
       </c>
       <c r="F17" t="n">
-        <v>5.176776390416514</v>
+        <v>6.659984893819685</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2199085567615926</v>
+        <v>0.09763414397046739</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3716019933538604</v>
+        <v>-0.6312873357140929</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6793143242575437</v>
+        <v>-0.7886449688726421</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5010755780902652</v>
+        <v>-0.7534495132780028</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01772280959669069</v>
+        <v>-0.0366959264513639</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5794780501992773</v>
+        <v>-0.3214884081708506</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.04761516853925527</v>
+        <v>-0.02649080878804166</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>52.7844107002762</v>
+        <v>74.44305246730869</v>
       </c>
       <c r="B18" t="n">
-        <v>117.2472561461711</v>
+        <v>123.3931895637954</v>
       </c>
       <c r="C18" t="n">
-        <v>47.54221040157736</v>
+        <v>45.50004555611457</v>
       </c>
       <c r="D18" t="n">
-        <v>9.876077602247172</v>
+        <v>8.805681456436014</v>
       </c>
       <c r="E18" t="n">
-        <v>2.60708017475383</v>
+        <v>4.544945156323855</v>
       </c>
       <c r="F18" t="n">
-        <v>5.392136394492486</v>
+        <v>8.331706768606407</v>
       </c>
       <c r="G18" t="n">
-        <v>0.187260830054248</v>
+        <v>0.05236212767567639</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4676133555042318</v>
+        <v>-0.7768385125382836</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.716661863881114</v>
+        <v>-0.8606224393932151</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5980615765419227</v>
+        <v>-0.8733530521230494</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0103382035141398</v>
+        <v>-0.004726938151048549</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2914968864868324</v>
+        <v>-0.4054067488295744</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.02997128248731095</v>
+        <v>-1.012358101515343e-05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>79.28978636459406</v>
+        <v>54.74526407383105</v>
       </c>
       <c r="B19" t="n">
-        <v>116.0354528715879</v>
+        <v>120.3630048046844</v>
       </c>
       <c r="C19" t="n">
-        <v>46.89327776444081</v>
+        <v>45.50030408624541</v>
       </c>
       <c r="D19" t="n">
-        <v>8.477471585780682</v>
+        <v>10.44414288557375</v>
       </c>
       <c r="E19" t="n">
-        <v>2.301406107499663</v>
+        <v>4.910761913841567</v>
       </c>
       <c r="F19" t="n">
-        <v>9.139262322318764</v>
+        <v>5.669261754857043</v>
       </c>
       <c r="G19" t="n">
-        <v>0.04285502002033475</v>
+        <v>0.1612445225355588</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8368431032498534</v>
+        <v>-0.4515332582702792</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8935139462782575</v>
+        <v>-0.7095634151239852</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9162348816763749</v>
+        <v>-0.5821678031424139</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1329194864809704</v>
+        <v>-0.02236028993108937</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4673002330155921</v>
+        <v>-0.2650600065260462</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.05093280591712577</v>
+        <v>-6.75747212020017e-05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>53.76905930286524</v>
+        <v>50.5439078171845</v>
       </c>
       <c r="B20" t="n">
-        <v>118.0299356252459</v>
+        <v>120.8608568359609</v>
       </c>
       <c r="C20" t="n">
-        <v>47.67364517876063</v>
+        <v>45.50042667654558</v>
       </c>
       <c r="D20" t="n">
-        <v>9.996737571962306</v>
+        <v>10.88417460822924</v>
       </c>
       <c r="E20" t="n">
-        <v>2.301406107499663</v>
+        <v>4.60136269168602</v>
       </c>
       <c r="F20" t="n">
-        <v>5.506651606412789</v>
+        <v>5.238224915214792</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1752945158315731</v>
+        <v>0.2183574689803223</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4954014281891588</v>
+        <v>-0.305360324923318</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7283586939701205</v>
+        <v>-0.6504120951587459</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6256107906166062</v>
+        <v>-0.4279067978002207</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.02833968834093665</v>
+        <v>-0.04657011945428103</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2877282034522358</v>
+        <v>-0.2351253431974395</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0248640693732818</v>
+        <v>-9.481701012850619e-05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>62.93979260086964</v>
+        <v>53.61351098721625</v>
       </c>
       <c r="B21" t="n">
-        <v>117.905004894417</v>
+        <v>127.8987706978432</v>
       </c>
       <c r="C21" t="n">
-        <v>47.66611581692879</v>
+        <v>45.50026129815231</v>
       </c>
       <c r="D21" t="n">
-        <v>9.879792865192485</v>
+        <v>10.9038108289855</v>
       </c>
       <c r="E21" t="n">
-        <v>2.784076622441731</v>
+        <v>4.40916467108395</v>
       </c>
       <c r="F21" t="n">
-        <v>6.705867288830729</v>
+        <v>5.618900894650324</v>
       </c>
       <c r="G21" t="n">
-        <v>0.09820311671617613</v>
+        <v>0.1750711077317147</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6815499146079435</v>
+        <v>-0.4161375882838186</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8125123772585776</v>
+        <v>-0.6947770970496864</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7967501444240587</v>
+        <v>-0.5458474343119841</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.121445975135456</v>
+        <v>-0.08858235594912879</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3451646395164806</v>
+        <v>-0.2569962657839158</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.02507827265690766</v>
+        <v>-5.806625606979976e-05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>98.20798884305449</v>
+        <v>93.11800645589324</v>
       </c>
       <c r="B22" t="n">
-        <v>105.7369221892652</v>
+        <v>108.05963380854</v>
       </c>
       <c r="C22" t="n">
-        <v>46.20679700338357</v>
+        <v>45.52333361491539</v>
       </c>
       <c r="D22" t="n">
-        <v>6.151358864448614</v>
+        <v>7.958838809884475</v>
       </c>
       <c r="E22" t="n">
-        <v>4.71793723545962</v>
+        <v>4.16207205007233</v>
       </c>
       <c r="F22" t="n">
-        <v>12.56506763613189</v>
+        <v>11.8456457059315</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02072879246109706</v>
+        <v>0.02438496680758279</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9110047789226776</v>
+        <v>-0.8822905067099885</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9384156992004699</v>
+        <v>-0.9202881626958833</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.962408687586942</v>
+        <v>-0.9456660159782579</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.0976585500577087</v>
+        <v>-0.2212465374269809</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6086205246948221</v>
+        <v>-0.5384657959982393</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.04394578602880959</v>
+        <v>-0.005185247758977274</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>54.79093635711155</v>
+        <v>84.23524010369917</v>
       </c>
       <c r="B23" t="n">
-        <v>118.0299356252459</v>
+        <v>134.4828823331382</v>
       </c>
       <c r="C23" t="n">
-        <v>47.67365507132028</v>
+        <v>45.61545579346861</v>
       </c>
       <c r="D23" t="n">
-        <v>9.903759672831221</v>
+        <v>8.271617268271687</v>
       </c>
       <c r="E23" t="n">
-        <v>2.2939285975876</v>
+        <v>4.722250548187433</v>
       </c>
       <c r="F23" t="n">
-        <v>5.582226558426004</v>
+        <v>10.05718931876118</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1635914581672084</v>
+        <v>0.03411877579736834</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5224174496389029</v>
+        <v>-0.843549206990228</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7399540307079552</v>
+        <v>-0.8973343724833791</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6519653319197297</v>
+        <v>-0.9208594405968655</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.001717617432048937</v>
+        <v>-0.08771603887752688</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.2842921151563478</v>
+        <v>-0.4751760857388565</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0248639434966279</v>
+        <v>-0.02565684299302429</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>44.15148007310714</v>
+        <v>45.13637678222848</v>
       </c>
       <c r="B24" t="n">
-        <v>118.2156538381544</v>
+        <v>119.6622784384119</v>
       </c>
       <c r="C24" t="n">
-        <v>47.7677891671331</v>
+        <v>45.50341625859291</v>
       </c>
       <c r="D24" t="n">
-        <v>6.966940294925411</v>
+        <v>7.070636852872784</v>
       </c>
       <c r="E24" t="n">
-        <v>3.349453238882417</v>
+        <v>4.911768627109637</v>
       </c>
       <c r="F24" t="n">
-        <v>4.4728430672873</v>
+        <v>4.647993183470112</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3428323684471025</v>
+        <v>0.3083212286758467</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1124562842503362</v>
+        <v>-0.04768401521084612</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5807435058498467</v>
+        <v>-0.5572886957886419</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.2104125253962624</v>
+        <v>-0.1340527967023936</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.003929635748574949</v>
+        <v>-0.002458060369697563</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.5319256997665671</v>
+        <v>-0.5358637196207805</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.02338865746618661</v>
+        <v>-0.0007591685762003975</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>47.78019120148866</v>
+        <v>89.61163727413307</v>
       </c>
       <c r="B25" t="n">
-        <v>109.7106499202194</v>
+        <v>108.05963380854</v>
       </c>
       <c r="C25" t="n">
-        <v>47.53891607820177</v>
+        <v>45.52333361491539</v>
       </c>
       <c r="D25" t="n">
-        <v>6.476903483609821</v>
+        <v>7.722607413085695</v>
       </c>
       <c r="E25" t="n">
-        <v>2.218937870687361</v>
+        <v>4.277969751452993</v>
       </c>
       <c r="F25" t="n">
-        <v>4.915217717288574</v>
+        <v>11.04242489356451</v>
       </c>
       <c r="G25" t="n">
-        <v>0.2533980203188835</v>
+        <v>0.02764848497218205</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.297630933517695</v>
+        <v>-0.8688669000529354</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6502131766786367</v>
+        <v>-0.9122008286468402</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4215803382084973</v>
+        <v>-0.937340227835133</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.01185280687415301</v>
+        <v>-0.0855995559013893</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.5672634310977805</v>
+        <v>-0.5134829155781981</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.03010137491802193</v>
+        <v>-0.005185247758977274</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>55.7886730163643</v>
+        <v>52.98745660433268</v>
       </c>
       <c r="B26" t="n">
-        <v>118.239330948559</v>
+        <v>121.408955523677</v>
       </c>
       <c r="C26" t="n">
-        <v>47.67365507132028</v>
+        <v>45.50312270123731</v>
       </c>
       <c r="D26" t="n">
-        <v>9.833235790205247</v>
+        <v>10.48882940563878</v>
       </c>
       <c r="E26" t="n">
-        <v>2.567057709386</v>
+        <v>4.86472243782729</v>
       </c>
       <c r="F26" t="n">
-        <v>5.696500547464916</v>
+        <v>5.455444160272981</v>
       </c>
       <c r="G26" t="n">
-        <v>0.152876483651648</v>
+        <v>0.1821960611353238</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5471072832832253</v>
+        <v>-0.3961830788666839</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7507449751119464</v>
+        <v>-0.6867466320836498</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.6756648646846828</v>
+        <v>-0.5252238053821302</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.002810567895995141</v>
+        <v>-0.00683503141210169</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.2917452775730836</v>
+        <v>-0.2525356283058703</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.0248639434966279</v>
+        <v>-0.000693933608291869</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>44.47780499215754</v>
+        <v>70.33083900191914</v>
       </c>
       <c r="B27" t="n">
-        <v>116.0255094915218</v>
+        <v>95.45038078387523</v>
       </c>
       <c r="C27" t="n">
-        <v>47.68252593708785</v>
+        <v>45.50561812995476</v>
       </c>
       <c r="D27" t="n">
-        <v>6.803764836549172</v>
+        <v>9.77139281404221</v>
       </c>
       <c r="E27" t="n">
-        <v>2.359531214288718</v>
+        <v>4.459884313463509</v>
       </c>
       <c r="F27" t="n">
-        <v>4.50800838991586</v>
+        <v>7.828311636265122</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3325751654138263</v>
+        <v>0.06440646698325442</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.1320275321682596</v>
+        <v>-0.7365223473947308</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.5879503548918665</v>
+        <v>-0.8396404173292077</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.2335739745376191</v>
+        <v>-0.8421181140155467</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.01278155677513055</v>
+        <v>-0.1272157723502811</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.5453353819787612</v>
+        <v>-0.3761072278886739</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.02475106726039901</v>
+        <v>-0.001248473323280791</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>61.82477714458506</v>
+        <v>71.08161363179333</v>
       </c>
       <c r="B28" t="n">
-        <v>116.0845923600903</v>
+        <v>124.599167867085</v>
       </c>
       <c r="C28" t="n">
-        <v>47.60167660278283</v>
+        <v>45.50575036268855</v>
       </c>
       <c r="D28" t="n">
-        <v>9.558909379123953</v>
+        <v>10.86960259249401</v>
       </c>
       <c r="E28" t="n">
-        <v>2.066955385140984</v>
+        <v>4.922515723248567</v>
       </c>
       <c r="F28" t="n">
-        <v>6.473133654016606</v>
+        <v>8.178281587961107</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1045064262116986</v>
+        <v>0.06251528354866398</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.6647693712510687</v>
+        <v>-0.7439634210681303</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8045354107814199</v>
+        <v>-0.8432539875679879</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.7824600372736765</v>
+        <v>-0.8479255256963402</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.04214561958774703</v>
+        <v>-0.3037365264442067</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.3368353963080734</v>
+        <v>-0.3814564971265275</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.02762296941116471</v>
+        <v>-0.00127785837523306</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>85.17251564380645</v>
+        <v>47.51448199991905</v>
       </c>
       <c r="B29" t="n">
-        <v>121.4368034604803</v>
+        <v>121.5600032944098</v>
       </c>
       <c r="C29" t="n">
-        <v>47.71927544624099</v>
+        <v>45.50347972995545</v>
       </c>
       <c r="D29" t="n">
-        <v>7.852788331825272</v>
+        <v>10.79036909445679</v>
       </c>
       <c r="E29" t="n">
-        <v>2.917837829774926</v>
+        <v>4.881780048761797</v>
       </c>
       <c r="F29" t="n">
-        <v>10.12768741148411</v>
+        <v>4.869200006885952</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03343287297660802</v>
+        <v>0.2755444582557528</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.8670259149931984</v>
+        <v>-0.1772581283559637</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.911122135775959</v>
+        <v>-0.603503816805516</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.93609864184775</v>
+        <v>-0.2860055197861729</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.1491356457568248</v>
+        <v>-0.02325157854918725</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.5112446309336703</v>
+        <v>-0.2313586149993929</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.02428345266841397</v>
+        <v>-0.0007732733234352973</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>48.98648216997409</v>
+        <v>67.82443132815283</v>
       </c>
       <c r="B30" t="n">
-        <v>87.123950984217</v>
+        <v>133.2081665388004</v>
       </c>
       <c r="C30" t="n">
-        <v>47.68430426715205</v>
+        <v>43.01313425259691</v>
       </c>
       <c r="D30" t="n">
-        <v>6.306328247849461</v>
+        <v>9.823784845498054</v>
       </c>
       <c r="E30" t="n">
-        <v>2.45147696655334</v>
+        <v>4.725688610032286</v>
       </c>
       <c r="F30" t="n">
-        <v>5.061070386239137</v>
+        <v>7.511059441001889</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2305733732645747</v>
+        <v>0.07354814027560684</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3474905542134383</v>
+        <v>-0.7070105686607289</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6697502321429087</v>
+        <v>-0.8248134809240513</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4755097653138902</v>
+        <v>-0.8182210078395958</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.0009981423635091408</v>
+        <v>-0.04559038499027981</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.5752732778970547</v>
+        <v>-0.3582490732130889</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.02472843911905633</v>
+        <v>-0.3427761610716969</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>64.93959612793809</v>
+        <v>86.28979474314467</v>
       </c>
       <c r="B31" t="n">
-        <v>117.4411143297097</v>
+        <v>127.7766657770583</v>
       </c>
       <c r="C31" t="n">
-        <v>47.67015768056513</v>
+        <v>45.53702384400034</v>
       </c>
       <c r="D31" t="n">
-        <v>9.687989305551277</v>
+        <v>8.820709409226138</v>
       </c>
       <c r="E31" t="n">
-        <v>2.453916342803741</v>
+        <v>4.599558708907015</v>
       </c>
       <c r="F31" t="n">
-        <v>6.964859657096651</v>
+        <v>10.57953790743738</v>
       </c>
       <c r="G31" t="n">
-        <v>0.08753106182271946</v>
+        <v>0.031544791432951</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7093525496433304</v>
+        <v>-0.853796863309761</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8261189633540983</v>
+        <v>-0.9032106803723121</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.8199572507386719</v>
+        <v>-0.9276263622273437</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1183070536327547</v>
+        <v>-0.2354398454051028</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.3601033113098626</v>
+        <v>-0.4898147875449058</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.02491865995192889</v>
+        <v>-0.008227520888966361</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>88.14565321085956</v>
+        <v>51.21572409726351</v>
       </c>
       <c r="B32" t="n">
-        <v>117.312158628642</v>
+        <v>148.7896706442193</v>
       </c>
       <c r="C32" t="n">
-        <v>47.57038047990051</v>
+        <v>45.50006051824526</v>
       </c>
       <c r="D32" t="n">
-        <v>7.408493443299062</v>
+        <v>10.61894673785983</v>
       </c>
       <c r="E32" t="n">
-        <v>2.119781643334987</v>
+        <v>4.953991512701093</v>
       </c>
       <c r="F32" t="n">
-        <v>10.6377172291015</v>
+        <v>5.26444068032748</v>
       </c>
       <c r="G32" t="n">
-        <v>0.02972323776375969</v>
+        <v>0.207227044374805</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8793882467265154</v>
+        <v>-0.3323257825242094</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9185895334366984</v>
+        <v>-0.661104323070153</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.943834981530808</v>
+        <v>-0.4573219675561295</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.1220376187915582</v>
+        <v>-0.007403737112328517</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.5334541758762624</v>
+        <v>-0.2399120341930026</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.02885884950956418</v>
+        <v>-1.344849894627242e-05</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>86.82158074558154</v>
+        <v>87.915663026942</v>
       </c>
       <c r="B33" t="n">
-        <v>117.4232431753159</v>
+        <v>121.4133768093612</v>
       </c>
       <c r="C33" t="n">
-        <v>47.71927544624099</v>
+        <v>45.50430998605204</v>
       </c>
       <c r="D33" t="n">
-        <v>7.778965201041594</v>
+        <v>7.958838809884475</v>
       </c>
       <c r="E33" t="n">
-        <v>3.085925340905295</v>
+        <v>4.527787781229257</v>
       </c>
       <c r="F33" t="n">
-        <v>10.44392267956881</v>
+        <v>10.73543319362053</v>
       </c>
       <c r="G33" t="n">
-        <v>0.03133005222319214</v>
+        <v>0.0294985097741585</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8740583157120366</v>
+        <v>-0.8615275462017337</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.915336508031341</v>
+        <v>-0.9078255382953891</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9405266614546213</v>
+        <v>-0.93266025642446</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.1734613964619105</v>
+        <v>-0.09879940593194587</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5235632622331415</v>
+        <v>-0.5013990990669617</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.02428345266841397</v>
+        <v>-0.0009577746782317431</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>46.37373258156187</v>
+        <v>48.37945518287518</v>
       </c>
       <c r="B34" t="n">
-        <v>109.3289046561658</v>
+        <v>124.745762019174</v>
       </c>
       <c r="C34" t="n">
-        <v>48.22836200206054</v>
+        <v>45.503358917479</v>
       </c>
       <c r="D34" t="n">
-        <v>6.605878099100174</v>
+        <v>10.7956237075566</v>
       </c>
       <c r="E34" t="n">
-        <v>4.835593282083368</v>
+        <v>4.713430807817049</v>
       </c>
       <c r="F34" t="n">
-        <v>4.745945455319982</v>
+        <v>4.967988183988734</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2838185922768708</v>
+        <v>0.2573547105311242</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2327914561553704</v>
+        <v>-0.2096910992233296</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6253808418666568</v>
+        <v>-0.6137063915597768</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.3495388071213217</v>
+        <v>-0.3208902144400411</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.02139363226774433</v>
+        <v>-0.003212109548386251</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.5579244586861106</v>
+        <v>-0.2197036181779857</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.001079771569545449</v>
+        <v>-0.0007464261064445143</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>50.45617990197253</v>
+        <v>44.55059538887077</v>
       </c>
       <c r="B35" t="n">
-        <v>89.8402405510908</v>
+        <v>125.3987076032305</v>
       </c>
       <c r="C35" t="n">
-        <v>46.63014497423041</v>
+        <v>45.50005252204506</v>
       </c>
       <c r="D35" t="n">
-        <v>6.255694526729703</v>
+        <v>10.89800432846986</v>
       </c>
       <c r="E35" t="n">
-        <v>2.060844648695323</v>
+        <v>4.449401416464278</v>
       </c>
       <c r="F35" t="n">
-        <v>5.280943194777394</v>
+        <v>4.569604007047513</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2064726675142719</v>
+        <v>0.3524998076094346</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4018363388063787</v>
+        <v>-0.004414161941685434</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.691494664268268</v>
+        <v>-0.5410397812596941</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.5327209641619068</v>
+        <v>-0.07991823773727987</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.01263753523741456</v>
+        <v>-0.003034024061941959</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5850321619325778</v>
+        <v>-0.2091294654165308</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.04910909106402327</v>
+        <v>-1.167156556847182e-05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>46.16740368740719</v>
+        <v>46.82771074647531</v>
       </c>
       <c r="B36" t="n">
-        <v>110.2918761710458</v>
+        <v>121.499185493538</v>
       </c>
       <c r="C36" t="n">
-        <v>47.68436930415007</v>
+        <v>45.64886529924043</v>
       </c>
       <c r="D36" t="n">
-        <v>6.605878099100174</v>
+        <v>10.69801041972323</v>
       </c>
       <c r="E36" t="n">
-        <v>4.853596560309255</v>
+        <v>4.451322787508889</v>
       </c>
       <c r="F36" t="n">
-        <v>4.705472278549441</v>
+        <v>4.780956440834458</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2885325737627591</v>
+        <v>0.2910201471456623</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.2226903241183196</v>
+        <v>-0.1411529106131984</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6215825795856547</v>
+        <v>-0.5901872993257246</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.3381451695507874</v>
+        <v>-0.2440695971592322</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.004056895893742066</v>
+        <v>-7.702507734502431e-05</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.556554422040211</v>
+        <v>-0.2262078305985649</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.02472761156380431</v>
+        <v>-0.03308117760898427</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>50.7865491537676</v>
+        <v>45.23906068005613</v>
       </c>
       <c r="B37" t="n">
-        <v>101.088932228479</v>
+        <v>111.9487109846687</v>
       </c>
       <c r="C37" t="n">
-        <v>47.64226172817931</v>
+        <v>45.52338846143331</v>
       </c>
       <c r="D37" t="n">
-        <v>6.266106026276246</v>
+        <v>7.070636852872784</v>
       </c>
       <c r="E37" t="n">
-        <v>2.62628633837036</v>
+        <v>4.8766684583174</v>
       </c>
       <c r="F37" t="n">
-        <v>5.336006047294388</v>
+        <v>4.66320580676742</v>
       </c>
       <c r="G37" t="n">
-        <v>0.2015349826257035</v>
+        <v>0.305695169546166</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.4131873655727102</v>
+        <v>-0.05405518936080503</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6961006044965787</v>
+        <v>-0.5595553896651292</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.5444579024327306</v>
+        <v>-0.1417446082119203</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.04785579685405599</v>
+        <v>-0.005604313516552307</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.5872258342415002</v>
+        <v>-0.5365140509736888</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.02602026772964526</v>
+        <v>-0.005197435874067374</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>42.99369101932709</v>
+        <v>67.67538738830793</v>
       </c>
       <c r="B38" t="n">
-        <v>115.4539497343753</v>
+        <v>132.9930584935006</v>
       </c>
       <c r="C38" t="n">
-        <v>47.75760205190434</v>
+        <v>43.01313425259691</v>
       </c>
       <c r="D38" t="n">
-        <v>6.965822996521692</v>
+        <v>9.823784845498054</v>
       </c>
       <c r="E38" t="n">
-        <v>3.796422023706307</v>
+        <v>4.725688610032286</v>
       </c>
       <c r="F38" t="n">
-        <v>4.341784690402165</v>
+        <v>7.487267264290194</v>
       </c>
       <c r="G38" t="n">
-        <v>0.3786881879084275</v>
+        <v>0.0741301776166754</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.04022240621624509</v>
+        <v>-0.7051315457529346</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.5548973810280713</v>
+        <v>-0.8238871584491658</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.123919712764123</v>
+        <v>-0.816673623387234</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.0192074539039376</v>
+        <v>-0.04315409124276647</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5354807732105636</v>
+        <v>-0.3571871351416939</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.02378057617794165</v>
+        <v>-0.3427761610716969</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>71.92053028464451</v>
+        <v>56.02100487104146</v>
       </c>
       <c r="B39" t="n">
-        <v>101.5083539815677</v>
+        <v>126.2987008317916</v>
       </c>
       <c r="C39" t="n">
-        <v>45.17005194569917</v>
+        <v>45.50575181051571</v>
       </c>
       <c r="D39" t="n">
-        <v>8.768566595565016</v>
+        <v>10.44972336303261</v>
       </c>
       <c r="E39" t="n">
-        <v>4.116888579337404</v>
+        <v>4.912593249828581</v>
       </c>
       <c r="F39" t="n">
-        <v>7.886798311116686</v>
+        <v>5.837136338152966</v>
       </c>
       <c r="G39" t="n">
-        <v>0.06033100200920757</v>
+        <v>0.148030276975329</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.7840830073963744</v>
+        <v>-0.4874299377097009</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.8645122815133455</v>
+        <v>-0.7246890472280179</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.8786197540900366</v>
+        <v>-0.6180954558695471</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.00795791521006704</v>
+        <v>-0.04096745669261085</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.4122513762405821</v>
+        <v>-0.2741496597061703</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.05862529123194947</v>
+        <v>-0.001278180114603067</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>42.99369101932709</v>
+        <v>55.57102789676275</v>
       </c>
       <c r="B40" t="n">
-        <v>98.40872197457733</v>
+        <v>145.8979141310429</v>
       </c>
       <c r="C40" t="n">
-        <v>47.75760205190434</v>
+        <v>45.52430093216981</v>
       </c>
       <c r="D40" t="n">
-        <v>6.965822996521692</v>
+        <v>10.61894673785983</v>
       </c>
       <c r="E40" t="n">
-        <v>3.879357680377084</v>
+        <v>4.990221141429499</v>
       </c>
       <c r="F40" t="n">
-        <v>4.341784690402165</v>
+        <v>5.81351878602465</v>
       </c>
       <c r="G40" t="n">
-        <v>0.3786881879084275</v>
+        <v>0.1527745442248585</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.04022240621624509</v>
+        <v>-0.4749294261742747</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.5548973810280713</v>
+        <v>-0.7193420849163217</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.123919712764123</v>
+        <v>-0.6056361909901087</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.0192074539039376</v>
+        <v>-0.0656137819147766</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.5354807732105636</v>
+        <v>-0.2709435737644346</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.02378057617794165</v>
+        <v>-0.005400207148846675</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>71.72677418957463</v>
+        <v>66.04547649901949</v>
       </c>
       <c r="B41" t="n">
-        <v>112.1015699446659</v>
+        <v>100.9148201627582</v>
       </c>
       <c r="C41" t="n">
-        <v>47.7570987159528</v>
+        <v>45.69310040870087</v>
       </c>
       <c r="D41" t="n">
-        <v>8.536228482434339</v>
+        <v>9.952228881168566</v>
       </c>
       <c r="E41" t="n">
-        <v>2.200924839089041</v>
+        <v>4.998992700657508</v>
       </c>
       <c r="F41" t="n">
-        <v>7.805082463056162</v>
+        <v>7.185232904529084</v>
       </c>
       <c r="G41" t="n">
-        <v>0.06080365397280055</v>
+        <v>0.08077533649652108</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.7824934237491046</v>
+        <v>-0.6836074194871925</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.86370045045348</v>
+        <v>-0.8134224309711571</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8774472414767976</v>
+        <v>-0.7987414129381945</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.005799584144747977</v>
+        <v>-0.09770868917643456</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.410804004699809</v>
+        <v>-0.3455740200555139</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.02379994051939377</v>
+        <v>-0.04291120193352788</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>64.73575418910725</v>
+        <v>65.99165936139264</v>
       </c>
       <c r="B42" t="n">
-        <v>114.1654335550461</v>
+        <v>126.3775095467388</v>
       </c>
       <c r="C42" t="n">
-        <v>47.72714128549919</v>
+        <v>45.50015582667587</v>
       </c>
       <c r="D42" t="n">
-        <v>9.201336544914302</v>
+        <v>9.906676465173456</v>
       </c>
       <c r="E42" t="n">
-        <v>3.972334903737052</v>
+        <v>4.999233012397795</v>
       </c>
       <c r="F42" t="n">
-        <v>6.827559875238213</v>
+        <v>7.158893591594815</v>
       </c>
       <c r="G42" t="n">
-        <v>0.08816082816500231</v>
+        <v>0.08095669927308335</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.7069894171532343</v>
+        <v>-0.6829128052426496</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.8250427425815577</v>
+        <v>-0.8131028103060276</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.8180581333384549</v>
+        <v>-0.7981638524573103</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.02043473914906974</v>
+        <v>-0.08478049983889124</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.35858059781291</v>
+        <v>-0.3451905729499225</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.02418336476791945</v>
+        <v>-3.46281501938106e-05</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>43.58691939686923</v>
+        <v>46.74903192988594</v>
       </c>
       <c r="B43" t="n">
-        <v>117.8614668914259</v>
+        <v>121.499185493538</v>
       </c>
       <c r="C43" t="n">
-        <v>47.55950274924839</v>
+        <v>45.64467896737232</v>
       </c>
       <c r="D43" t="n">
-        <v>6.975251858962958</v>
+        <v>10.72902435674198</v>
       </c>
       <c r="E43" t="n">
-        <v>2.599504417562517</v>
+        <v>4.440630563627236</v>
       </c>
       <c r="F43" t="n">
-        <v>4.422746290855328</v>
+        <v>4.778451452175625</v>
       </c>
       <c r="G43" t="n">
-        <v>0.3595044026581208</v>
+        <v>0.2929789007785468</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.07831949635904119</v>
+        <v>-0.1368343520280779</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.5684814561295422</v>
+        <v>-0.5885970113173712</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.1698436829204487</v>
+        <v>-0.2390030497437859</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.0339555400033263</v>
+        <v>-0.004668647811566551</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.5394198464070251</v>
+        <v>-0.2256177394741445</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.02928840977424129</v>
+        <v>-0.03215088163829455</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>96.28352150550394</v>
+        <v>51.73869367977091</v>
       </c>
       <c r="B44" t="n">
-        <v>101.0262499618137</v>
+        <v>148.4959098572799</v>
       </c>
       <c r="C44" t="n">
-        <v>47.57521438919512</v>
+        <v>45.52430093216981</v>
       </c>
       <c r="D44" t="n">
-        <v>6.151690327940125</v>
+        <v>10.61894673785983</v>
       </c>
       <c r="E44" t="n">
-        <v>2.545968404107387</v>
+        <v>4.990221141429499</v>
       </c>
       <c r="F44" t="n">
-        <v>12.12983320857683</v>
+        <v>5.329030160713584</v>
       </c>
       <c r="G44" t="n">
-        <v>0.02209750051857405</v>
+        <v>0.1994833261727241</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.9059735950016277</v>
+        <v>-0.352019585624485</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.9352217728386375</v>
+        <v>-0.6689228767491229</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.9595809258200728</v>
+        <v>-0.4784900574274137</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.04788976365284567</v>
+        <v>-0.01485346769977837</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.5942446194903268</v>
+        <v>-0.2436381924683677</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.0286679590175646</v>
+        <v>-0.005400207148846675</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>43.58691939686923</v>
+        <v>62.99119629337329</v>
       </c>
       <c r="B45" t="n">
-        <v>83.99280081622027</v>
+        <v>124.8915300244221</v>
       </c>
       <c r="C45" t="n">
-        <v>47.55950274924839</v>
+        <v>45.61920863954618</v>
       </c>
       <c r="D45" t="n">
-        <v>6.975251858962958</v>
+        <v>9.906676465173456</v>
       </c>
       <c r="E45" t="n">
-        <v>2.593094084283945</v>
+        <v>4.713557012366493</v>
       </c>
       <c r="F45" t="n">
-        <v>4.422746290855328</v>
+        <v>6.708267565308997</v>
       </c>
       <c r="G45" t="n">
-        <v>0.3595044026581208</v>
+        <v>0.09580991225039528</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.07831949635904119</v>
+        <v>-0.6368329966616431</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5684814561295422</v>
+        <v>-0.791226474332182</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.1698436829204487</v>
+        <v>-0.7583576505725704</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.0339555400033263</v>
+        <v>-0.04164245975837478</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5394198464070251</v>
+        <v>-0.3238122735902846</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.02928840977424129</v>
+        <v>-0.02649080878804166</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>92.84596979597185</v>
+        <v>46.77179335400039</v>
       </c>
       <c r="B46" t="n">
-        <v>110.2579773731393</v>
+        <v>113.0851221305847</v>
       </c>
       <c r="C46" t="n">
-        <v>47.67746306996469</v>
+        <v>45.65250988414892</v>
       </c>
       <c r="D46" t="n">
-        <v>7.819664714357985</v>
+        <v>7.01787953082837</v>
       </c>
       <c r="E46" t="n">
-        <v>2.286481829712836</v>
+        <v>4.798116248166905</v>
       </c>
       <c r="F46" t="n">
-        <v>11.71680862963097</v>
+        <v>4.878002237000467</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02506988906347058</v>
+        <v>0.2695923723012675</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.8957101071254004</v>
+        <v>-0.142777277732624</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.9286250754475828</v>
+        <v>-0.5916100014356691</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.9536403427821063</v>
+        <v>-0.247064386609196</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.3278837673669724</v>
+        <v>-0.03443015010318257</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.5685658685198463</v>
+        <v>-0.5462213579086692</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.02481548908802686</v>
+        <v>-0.03389108536642663</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>60.63203496227922</v>
+        <v>64.28101911500002</v>
       </c>
       <c r="B47" t="n">
-        <v>117.8614668914259</v>
+        <v>100.9148201627582</v>
       </c>
       <c r="C47" t="n">
-        <v>43.2569775968105</v>
+        <v>45.5000609065822</v>
       </c>
       <c r="D47" t="n">
-        <v>10.02966639728932</v>
+        <v>9.906676465173456</v>
       </c>
       <c r="E47" t="n">
-        <v>2.718576383500054</v>
+        <v>4.998992700657508</v>
       </c>
       <c r="F47" t="n">
-        <v>6.397685117020543</v>
+        <v>6.896350757954885</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1126737248486993</v>
+        <v>0.08900435781202198</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.6448265884011666</v>
+        <v>-0.6616037430426061</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.7950215036465937</v>
+        <v>-0.8039584869049136</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.7650702382252755</v>
+        <v>-0.7805965588466386</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.02338594723767185</v>
+        <v>-0.08448926949781305</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.3279255290364077</v>
+        <v>-0.3450549522784376</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.08768748981963706</v>
+        <v>-1.353479604504493e-05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>94.33172775942029</v>
+        <v>83.90973885550711</v>
       </c>
       <c r="B48" t="n">
-        <v>117.6968014737866</v>
+        <v>128.1797245990278</v>
       </c>
       <c r="C48" t="n">
-        <v>46.14322563392956</v>
+        <v>45.52299814589642</v>
       </c>
       <c r="D48" t="n">
-        <v>6.758728330717523</v>
+        <v>7.945539263971446</v>
       </c>
       <c r="E48" t="n">
-        <v>2.860485441221509</v>
+        <v>4.54386901824003</v>
       </c>
       <c r="F48" t="n">
-        <v>11.81729138587784</v>
+        <v>9.922470704610966</v>
       </c>
       <c r="G48" t="n">
-        <v>0.0236809191643288</v>
+        <v>0.03450292873140889</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.9003772261467493</v>
+        <v>-0.8419006447062001</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.9316329388195087</v>
+        <v>-0.8964244508002071</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.9563709245571262</v>
+        <v>-0.9197646458211751</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.1210023992612897</v>
+        <v>-0.001807749960016089</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.5796645841086203</v>
+        <v>-0.4728568893454882</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.04494520188592436</v>
+        <v>-0.00511069908809253</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>83.36996026282053</v>
+        <v>48.18751018435644</v>
       </c>
       <c r="B49" t="n">
-        <v>117.312158628642</v>
+        <v>124.6653276764369</v>
       </c>
       <c r="C49" t="n">
-        <v>46.95395033660755</v>
+        <v>45.50003347480325</v>
       </c>
       <c r="D49" t="n">
-        <v>7.489168459781595</v>
+        <v>10.89942561471796</v>
       </c>
       <c r="E49" t="n">
-        <v>4.033401474871443</v>
+        <v>4.877411129213814</v>
       </c>
       <c r="F49" t="n">
-        <v>9.703793871768877</v>
+        <v>4.967243413383674</v>
       </c>
       <c r="G49" t="n">
-        <v>0.03587608057139477</v>
+        <v>0.2615371649693531</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.8587857608932966</v>
+        <v>-0.2001459458711515</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9062839803349335</v>
+        <v>-0.6100744967099819</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.9308215591306546</v>
+        <v>-0.3099185613667612</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.0009362612190450647</v>
+        <v>-0.01955978105357802</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.4977794165456264</v>
+        <v>-0.2183360100635396</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.05213151312512011</v>
+        <v>-7.438845166241048e-06</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>47.75116739525129</v>
+        <v>70.87945082554731</v>
       </c>
       <c r="B50" t="n">
-        <v>109.5257339122063</v>
+        <v>119.9536433670747</v>
       </c>
       <c r="C50" t="n">
-        <v>47.53891607820177</v>
+        <v>45.50575036268855</v>
       </c>
       <c r="D50" t="n">
-        <v>6.476903483609821</v>
+        <v>9.77139281404221</v>
       </c>
       <c r="E50" t="n">
-        <v>4.85975031404296</v>
+        <v>4.922515723248567</v>
       </c>
       <c r="F50" t="n">
-        <v>4.910894357948103</v>
+        <v>7.919584213827311</v>
       </c>
       <c r="G50" t="n">
-        <v>0.2539757669425772</v>
+        <v>0.06265521863536204</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.2963729098552751</v>
+        <v>-0.7423864365302423</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6497261430818793</v>
+        <v>-0.8426202038497627</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.4202036356406057</v>
+        <v>-0.8467580712826295</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01093607758969229</v>
+        <v>-0.1357849139267157</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.567070711225406</v>
+        <v>-0.3800160871320245</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.03010137491802193</v>
+        <v>-0.00127785837523306</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>81.94991618786833</v>
+        <v>64.28101911500002</v>
       </c>
       <c r="B51" t="n">
-        <v>101.4904412976586</v>
+        <v>96.94431812912339</v>
       </c>
       <c r="C51" t="n">
-        <v>46.73286203828516</v>
+        <v>45.5000609065822</v>
       </c>
       <c r="D51" t="n">
-        <v>7.811173290891712</v>
+        <v>9.906676465173456</v>
       </c>
       <c r="E51" t="n">
-        <v>3.989188911893903</v>
+        <v>4.998992700657508</v>
       </c>
       <c r="F51" t="n">
-        <v>9.494771687078696</v>
+        <v>6.896350757954885</v>
       </c>
       <c r="G51" t="n">
-        <v>0.03810536438996329</v>
+        <v>0.08900435781202198</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.8516514540909798</v>
+        <v>-0.6616037430426061</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.9020904178731625</v>
+        <v>-0.8039584869049136</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.9261566990931482</v>
+        <v>-0.7805965588466386</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.04179092613009096</v>
+        <v>-0.1102014856987223</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.4871715882861448</v>
+        <v>-0.3571076433625001</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.04982100019261953</v>
+        <v>-1.353479604504493e-05</v>
       </c>
     </row>
   </sheetData>
